--- a/03_Group_comparisons/Proteome/04_Module_Contrasts/c_data/module_contrasts_all_inputs.xlsx
+++ b/03_Group_comparisons/Proteome/04_Module_Contrasts/c_data/module_contrasts_all_inputs.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9233" uniqueCount="280">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9263" uniqueCount="299">
   <si>
     <t>sheet</t>
   </si>
@@ -329,34 +329,34 @@
     <t>limpa</t>
   </si>
   <si>
-    <t>03_Cluster_groups/Proteome/05_Module_Contrasts/T1/c_data/module_contrasts.xlsx</t>
+    <t>03_Group_comparisons/Proteome/04_Module_Contrasts/T1/c_data/module_contrasts.xlsx</t>
   </si>
   <si>
-    <t>72f50dedb7cdc4ac4110633928ee4501</t>
+    <t>1147f11c2e276e7b1bcef3f0095f4e56</t>
   </si>
   <si>
-    <t>03_Cluster_groups/Proteome/05_Module_Contrasts/T2/c_data/module_contrasts.xlsx</t>
+    <t>03_Group_comparisons/Proteome/04_Module_Contrasts/T2/c_data/module_contrasts.xlsx</t>
   </si>
   <si>
-    <t>53ca2db70a350e5b0db6e2ec7183fb17</t>
+    <t>15fd90b562e9350f21b6c1afab8dfcec</t>
   </si>
   <si>
-    <t>03_Cluster_groups/Proteome/05_Module_Contrasts/T3/c_data/module_contrasts.xlsx</t>
+    <t>03_Group_comparisons/Proteome/04_Module_Contrasts/T3/c_data/module_contrasts.xlsx</t>
   </si>
   <si>
-    <t>124c4005fbb33d2ddd6fbd49c71203b9</t>
+    <t>2f8060d200909be00dc63ea1bea733a1</t>
   </si>
   <si>
-    <t>03_Cluster_groups/Proteome/05_Module_Contrasts/training/c_data/module_contrasts.xlsx</t>
+    <t>03_Group_comparisons/Proteome/04_Module_Contrasts/training/c_data/module_contrasts.xlsx</t>
   </si>
   <si>
-    <t>398ca48bde264965b05bf5929819004c</t>
+    <t>839d591089f64d51b85e7130a52e12c5</t>
   </si>
   <si>
-    <t>03_Cluster_groups/Proteome/05_Module_Contrasts/acute/c_data/module_contrasts.xlsx</t>
+    <t>03_Group_comparisons/Proteome/04_Module_Contrasts/acute/c_data/module_contrasts.xlsx</t>
   </si>
   <si>
-    <t>f418e1f7c29ed622164abd856d7fb443</t>
+    <t>3c7d24d9d9b2dff684f52102256172d4</t>
   </si>
   <si>
     <t>BiocGenerics</t>
@@ -491,6 +491,12 @@
     <t>1.7-17</t>
   </si>
   <si>
+    <t>evaluate</t>
+  </si>
+  <si>
+    <t>1.0.5</t>
+  </si>
+  <si>
     <t>Exact</t>
   </si>
   <si>
@@ -510,6 +516,12 @@
   </si>
   <si>
     <t>2.1.2</t>
+  </si>
+  <si>
+    <t>fastmap</t>
+  </si>
+  <si>
+    <t>1.2.0</t>
   </si>
   <si>
     <t>forcats</t>
@@ -587,6 +599,18 @@
     <t>1.1.4</t>
   </si>
   <si>
+    <t>htmltools</t>
+  </si>
+  <si>
+    <t>0.5.9</t>
+  </si>
+  <si>
+    <t>htmlwidgets</t>
+  </si>
+  <si>
+    <t>1.6.4</t>
+  </si>
+  <si>
     <t>httr</t>
   </si>
   <si>
@@ -605,6 +629,18 @@
     <t>1.0.14</t>
   </si>
   <si>
+    <t>jsonlite</t>
+  </si>
+  <si>
+    <t>2.0.0</t>
+  </si>
+  <si>
+    <t>knitr</t>
+  </si>
+  <si>
+    <t>1.51</t>
+  </si>
+  <si>
     <t>labeling</t>
   </si>
   <si>
@@ -618,9 +654,6 @@
   </si>
   <si>
     <t>lifecycle</t>
-  </si>
-  <si>
-    <t>1.0.5</t>
   </si>
   <si>
     <t>limma</t>
@@ -672,6 +705,12 @@
   </si>
   <si>
     <t>3.1-169</t>
+  </si>
+  <si>
+    <t>otel</t>
+  </si>
+  <si>
+    <t>0.2.0</t>
   </si>
   <si>
     <t>pillar</t>
@@ -750,6 +789,12 @@
   </si>
   <si>
     <t>1.3.0</t>
+  </si>
+  <si>
+    <t>rmarkdown</t>
+  </si>
+  <si>
+    <t>2.31</t>
   </si>
   <si>
     <t>rootSolve</t>
@@ -861,6 +906,18 @@
   </si>
   <si>
     <t>2.0.1</t>
+  </si>
+  <si>
+    <t>xfun</t>
+  </si>
+  <si>
+    <t>0.57</t>
+  </si>
+  <si>
+    <t>yaml</t>
+  </si>
+  <si>
+    <t>2.3.12</t>
   </si>
 </sst>
 </file>
@@ -64821,7 +64878,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C85"/>
+  <dimension ref="A1:C95"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1">
@@ -65085,18 +65142,18 @@
         <v>159</v>
       </c>
       <c r="C24" t="s">
-        <v>160</v>
+        <v>117</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" t="s">
+        <v>160</v>
+      </c>
+      <c r="B25" t="s">
         <v>161</v>
       </c>
-      <c r="B25" t="s">
+      <c r="C25" t="s">
         <v>162</v>
-      </c>
-      <c r="C25" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -65181,7 +65238,7 @@
         <v>177</v>
       </c>
       <c r="B33" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="C33" t="s">
         <v>117</v>
@@ -65189,10 +65246,10 @@
     </row>
     <row r="34" spans="1:3">
       <c r="A34" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B34" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C34" t="s">
         <v>117</v>
@@ -65200,10 +65257,10 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B35" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="C35" t="s">
         <v>117</v>
@@ -65261,7 +65318,7 @@
         <v>191</v>
       </c>
       <c r="C40" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -65305,7 +65362,7 @@
         <v>199</v>
       </c>
       <c r="C44" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -65316,7 +65373,7 @@
         <v>201</v>
       </c>
       <c r="C45" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -65324,7 +65381,7 @@
         <v>202</v>
       </c>
       <c r="B46" t="s">
-        <v>157</v>
+        <v>203</v>
       </c>
       <c r="C46" t="s">
         <v>117</v>
@@ -65332,10 +65389,10 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B47" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C47" t="s">
         <v>117</v>
@@ -65343,10 +65400,10 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B48" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C48" t="s">
         <v>117</v>
@@ -65354,10 +65411,10 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B49" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C49" t="s">
         <v>117</v>
@@ -65365,10 +65422,10 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B50" t="s">
-        <v>210</v>
+        <v>157</v>
       </c>
       <c r="C50" t="s">
         <v>117</v>
@@ -65382,7 +65439,7 @@
         <v>212</v>
       </c>
       <c r="C51" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -65390,7 +65447,7 @@
         <v>213</v>
       </c>
       <c r="B52" t="s">
-        <v>214</v>
+        <v>159</v>
       </c>
       <c r="C52" t="s">
         <v>117</v>
@@ -65398,10 +65455,10 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53" t="s">
+        <v>214</v>
+      </c>
+      <c r="B53" t="s">
         <v>215</v>
-      </c>
-      <c r="B53" t="s">
-        <v>216</v>
       </c>
       <c r="C53" t="s">
         <v>117</v>
@@ -65409,10 +65466,10 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54" t="s">
+        <v>216</v>
+      </c>
+      <c r="B54" t="s">
         <v>217</v>
-      </c>
-      <c r="B54" t="s">
-        <v>218</v>
       </c>
       <c r="C54" t="s">
         <v>117</v>
@@ -65420,10 +65477,10 @@
     </row>
     <row r="55" spans="1:3">
       <c r="A55" t="s">
+        <v>218</v>
+      </c>
+      <c r="B55" t="s">
         <v>219</v>
-      </c>
-      <c r="B55" t="s">
-        <v>220</v>
       </c>
       <c r="C55" t="s">
         <v>117</v>
@@ -65431,10 +65488,10 @@
     </row>
     <row r="56" spans="1:3">
       <c r="A56" t="s">
+        <v>220</v>
+      </c>
+      <c r="B56" t="s">
         <v>221</v>
-      </c>
-      <c r="B56" t="s">
-        <v>222</v>
       </c>
       <c r="C56" t="s">
         <v>117</v>
@@ -65442,10 +65499,10 @@
     </row>
     <row r="57" spans="1:3">
       <c r="A57" t="s">
+        <v>222</v>
+      </c>
+      <c r="B57" t="s">
         <v>223</v>
-      </c>
-      <c r="B57" t="s">
-        <v>224</v>
       </c>
       <c r="C57" t="s">
         <v>117</v>
@@ -65453,10 +65510,10 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58" t="s">
+        <v>224</v>
+      </c>
+      <c r="B58" t="s">
         <v>225</v>
-      </c>
-      <c r="B58" t="s">
-        <v>226</v>
       </c>
       <c r="C58" t="s">
         <v>117</v>
@@ -65464,10 +65521,10 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59" t="s">
+        <v>226</v>
+      </c>
+      <c r="B59" t="s">
         <v>227</v>
-      </c>
-      <c r="B59" t="s">
-        <v>228</v>
       </c>
       <c r="C59" t="s">
         <v>117</v>
@@ -65475,10 +65532,10 @@
     </row>
     <row r="60" spans="1:3">
       <c r="A60" t="s">
+        <v>228</v>
+      </c>
+      <c r="B60" t="s">
         <v>229</v>
-      </c>
-      <c r="B60" t="s">
-        <v>230</v>
       </c>
       <c r="C60" t="s">
         <v>117</v>
@@ -65486,10 +65543,10 @@
     </row>
     <row r="61" spans="1:3">
       <c r="A61" t="s">
+        <v>230</v>
+      </c>
+      <c r="B61" t="s">
         <v>231</v>
-      </c>
-      <c r="B61" t="s">
-        <v>232</v>
       </c>
       <c r="C61" t="s">
         <v>117</v>
@@ -65497,10 +65554,10 @@
     </row>
     <row r="62" spans="1:3">
       <c r="A62" t="s">
+        <v>232</v>
+      </c>
+      <c r="B62" t="s">
         <v>233</v>
-      </c>
-      <c r="B62" t="s">
-        <v>234</v>
       </c>
       <c r="C62" t="s">
         <v>117</v>
@@ -65508,10 +65565,10 @@
     </row>
     <row r="63" spans="1:3">
       <c r="A63" t="s">
+        <v>234</v>
+      </c>
+      <c r="B63" t="s">
         <v>235</v>
-      </c>
-      <c r="B63" t="s">
-        <v>236</v>
       </c>
       <c r="C63" t="s">
         <v>117</v>
@@ -65519,10 +65576,10 @@
     </row>
     <row r="64" spans="1:3">
       <c r="A64" t="s">
+        <v>236</v>
+      </c>
+      <c r="B64" t="s">
         <v>237</v>
-      </c>
-      <c r="B64" t="s">
-        <v>238</v>
       </c>
       <c r="C64" t="s">
         <v>117</v>
@@ -65530,10 +65587,10 @@
     </row>
     <row r="65" spans="1:3">
       <c r="A65" t="s">
+        <v>238</v>
+      </c>
+      <c r="B65" t="s">
         <v>239</v>
-      </c>
-      <c r="B65" t="s">
-        <v>240</v>
       </c>
       <c r="C65" t="s">
         <v>117</v>
@@ -65541,21 +65598,21 @@
     </row>
     <row r="66" spans="1:3">
       <c r="A66" t="s">
+        <v>240</v>
+      </c>
+      <c r="B66" t="s">
         <v>241</v>
       </c>
-      <c r="B66" t="s">
-        <v>242</v>
-      </c>
       <c r="C66" t="s">
-        <v>160</v>
+        <v>117</v>
       </c>
     </row>
     <row r="67" spans="1:3">
       <c r="A67" t="s">
+        <v>242</v>
+      </c>
+      <c r="B67" t="s">
         <v>243</v>
-      </c>
-      <c r="B67" t="s">
-        <v>244</v>
       </c>
       <c r="C67" t="s">
         <v>117</v>
@@ -65563,10 +65620,10 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68" t="s">
+        <v>244</v>
+      </c>
+      <c r="B68" t="s">
         <v>245</v>
-      </c>
-      <c r="B68" t="s">
-        <v>246</v>
       </c>
       <c r="C68" t="s">
         <v>117</v>
@@ -65574,10 +65631,10 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69" t="s">
+        <v>246</v>
+      </c>
+      <c r="B69" t="s">
         <v>247</v>
-      </c>
-      <c r="B69" t="s">
-        <v>248</v>
       </c>
       <c r="C69" t="s">
         <v>117</v>
@@ -65585,21 +65642,21 @@
     </row>
     <row r="70" spans="1:3">
       <c r="A70" t="s">
+        <v>248</v>
+      </c>
+      <c r="B70" t="s">
         <v>249</v>
       </c>
-      <c r="B70" t="s">
-        <v>250</v>
-      </c>
       <c r="C70" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
     </row>
     <row r="71" spans="1:3">
       <c r="A71" t="s">
+        <v>250</v>
+      </c>
+      <c r="B71" t="s">
         <v>251</v>
-      </c>
-      <c r="B71" t="s">
-        <v>252</v>
       </c>
       <c r="C71" t="s">
         <v>117</v>
@@ -65607,10 +65664,10 @@
     </row>
     <row r="72" spans="1:3">
       <c r="A72" t="s">
+        <v>252</v>
+      </c>
+      <c r="B72" t="s">
         <v>253</v>
-      </c>
-      <c r="B72" t="s">
-        <v>254</v>
       </c>
       <c r="C72" t="s">
         <v>117</v>
@@ -65618,21 +65675,21 @@
     </row>
     <row r="73" spans="1:3">
       <c r="A73" t="s">
+        <v>254</v>
+      </c>
+      <c r="B73" t="s">
         <v>255</v>
       </c>
-      <c r="B73" t="s">
-        <v>256</v>
-      </c>
       <c r="C73" t="s">
-        <v>117</v>
+        <v>162</v>
       </c>
     </row>
     <row r="74" spans="1:3">
       <c r="A74" t="s">
+        <v>256</v>
+      </c>
+      <c r="B74" t="s">
         <v>257</v>
-      </c>
-      <c r="B74" t="s">
-        <v>258</v>
       </c>
       <c r="C74" t="s">
         <v>117</v>
@@ -65640,10 +65697,10 @@
     </row>
     <row r="75" spans="1:3">
       <c r="A75" t="s">
+        <v>258</v>
+      </c>
+      <c r="B75" t="s">
         <v>259</v>
-      </c>
-      <c r="B75" t="s">
-        <v>260</v>
       </c>
       <c r="C75" t="s">
         <v>117</v>
@@ -65651,10 +65708,10 @@
     </row>
     <row r="76" spans="1:3">
       <c r="A76" t="s">
+        <v>260</v>
+      </c>
+      <c r="B76" t="s">
         <v>261</v>
-      </c>
-      <c r="B76" t="s">
-        <v>262</v>
       </c>
       <c r="C76" t="s">
         <v>117</v>
@@ -65662,10 +65719,10 @@
     </row>
     <row r="77" spans="1:3">
       <c r="A77" t="s">
+        <v>262</v>
+      </c>
+      <c r="B77" t="s">
         <v>263</v>
-      </c>
-      <c r="B77" t="s">
-        <v>264</v>
       </c>
       <c r="C77" t="s">
         <v>117</v>
@@ -65673,21 +65730,21 @@
     </row>
     <row r="78" spans="1:3">
       <c r="A78" t="s">
+        <v>264</v>
+      </c>
+      <c r="B78" t="s">
         <v>265</v>
       </c>
-      <c r="B78" t="s">
-        <v>266</v>
-      </c>
       <c r="C78" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="79" spans="1:3">
       <c r="A79" t="s">
+        <v>266</v>
+      </c>
+      <c r="B79" t="s">
         <v>267</v>
-      </c>
-      <c r="B79" t="s">
-        <v>268</v>
       </c>
       <c r="C79" t="s">
         <v>117</v>
@@ -65695,10 +65752,10 @@
     </row>
     <row r="80" spans="1:3">
       <c r="A80" t="s">
+        <v>268</v>
+      </c>
+      <c r="B80" t="s">
         <v>269</v>
-      </c>
-      <c r="B80" t="s">
-        <v>153</v>
       </c>
       <c r="C80" t="s">
         <v>117</v>
@@ -65756,7 +65813,117 @@
         <v>279</v>
       </c>
       <c r="C85" t="s">
-        <v>160</v>
+        <v>117</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3">
+      <c r="A86" t="s">
+        <v>280</v>
+      </c>
+      <c r="B86" t="s">
+        <v>281</v>
+      </c>
+      <c r="C86" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3">
+      <c r="A87" t="s">
+        <v>282</v>
+      </c>
+      <c r="B87" t="s">
+        <v>283</v>
+      </c>
+      <c r="C87" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3">
+      <c r="A88" t="s">
+        <v>284</v>
+      </c>
+      <c r="B88" t="s">
+        <v>153</v>
+      </c>
+      <c r="C88" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3">
+      <c r="A89" t="s">
+        <v>285</v>
+      </c>
+      <c r="B89" t="s">
+        <v>286</v>
+      </c>
+      <c r="C89" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3">
+      <c r="A90" t="s">
+        <v>287</v>
+      </c>
+      <c r="B90" t="s">
+        <v>288</v>
+      </c>
+      <c r="C90" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3">
+      <c r="A91" t="s">
+        <v>289</v>
+      </c>
+      <c r="B91" t="s">
+        <v>290</v>
+      </c>
+      <c r="C91" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3">
+      <c r="A92" t="s">
+        <v>291</v>
+      </c>
+      <c r="B92" t="s">
+        <v>292</v>
+      </c>
+      <c r="C92" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3">
+      <c r="A93" t="s">
+        <v>293</v>
+      </c>
+      <c r="B93" t="s">
+        <v>294</v>
+      </c>
+      <c r="C93" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3">
+      <c r="A94" t="s">
+        <v>295</v>
+      </c>
+      <c r="B94" t="s">
+        <v>296</v>
+      </c>
+      <c r="C94" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3">
+      <c r="A95" t="s">
+        <v>297</v>
+      </c>
+      <c r="B95" t="s">
+        <v>298</v>
+      </c>
+      <c r="C95" t="s">
+        <v>117</v>
       </c>
     </row>
   </sheetData>

--- a/03_Group_comparisons/Proteome/04_Module_Contrasts/c_data/module_contrasts_all_inputs.xlsx
+++ b/03_Group_comparisons/Proteome/04_Module_Contrasts/c_data/module_contrasts_all_inputs.xlsx
@@ -332,31 +332,31 @@
     <t>03_Group_comparisons/Proteome/04_Module_Contrasts/T1/c_data/module_contrasts.xlsx</t>
   </si>
   <si>
-    <t>1147f11c2e276e7b1bcef3f0095f4e56</t>
+    <t>53c4968d608506cece73fe0546414026</t>
   </si>
   <si>
     <t>03_Group_comparisons/Proteome/04_Module_Contrasts/T2/c_data/module_contrasts.xlsx</t>
   </si>
   <si>
-    <t>15fd90b562e9350f21b6c1afab8dfcec</t>
+    <t>29ead3dad423c3cb5d969b769dab18f9</t>
   </si>
   <si>
     <t>03_Group_comparisons/Proteome/04_Module_Contrasts/T3/c_data/module_contrasts.xlsx</t>
   </si>
   <si>
-    <t>2f8060d200909be00dc63ea1bea733a1</t>
+    <t>a0a9bf144a2b5906d1376f1dc96676cf</t>
   </si>
   <si>
     <t>03_Group_comparisons/Proteome/04_Module_Contrasts/training/c_data/module_contrasts.xlsx</t>
   </si>
   <si>
-    <t>839d591089f64d51b85e7130a52e12c5</t>
+    <t>4d2011c7bc27a25a238c910eddd9e20e</t>
   </si>
   <si>
     <t>03_Group_comparisons/Proteome/04_Module_Contrasts/acute/c_data/module_contrasts.xlsx</t>
   </si>
   <si>
-    <t>3c7d24d9d9b2dff684f52102256172d4</t>
+    <t>d597e8226e4a5cd9f1dadacd14fb972f</t>
   </si>
   <si>
     <t>BiocGenerics</t>
